--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260205_202228.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
